--- a/e2e/expectedData/moju_Tunjangan_Kompetensi_Q1.xlsx
+++ b/e2e/expectedData/moju_Tunjangan_Kompetensi_Q1.xlsx
@@ -128,7 +128,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>DILI, 26 Agustus 2026</t>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -776,9 +776,7 @@
       <c r="C17" s="3">
         <v>51141005</v>
       </c>
-      <c r="D17" s="4">
-        <v>14.17</v>
-      </c>
+      <c r="D17" s="4"/>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5">
@@ -791,9 +789,7 @@
       <c r="C18" s="3">
         <v>51141005</v>
       </c>
-      <c r="D18" s="4">
-        <v>21.25</v>
-      </c>
+      <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5">
@@ -806,9 +802,7 @@
       <c r="C19" s="3">
         <v>51141005</v>
       </c>
-      <c r="D19" s="4">
-        <v>28.33</v>
-      </c>
+      <c r="D19" s="4"/>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5">
@@ -926,9 +920,7 @@
         <v>31</v>
       </c>
       <c r="D28" s="4"/>
-      <c r="E28" s="4">
-        <v>63.75</v>
-      </c>
+      <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3">
@@ -989,10 +981,10 @@
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="6">
-        <v>63.75</v>
+        <v>0.0</v>
       </c>
       <c r="E33" s="6">
-        <v>63.75</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35" spans="1:5">

--- a/e2e/expectedData/moju_Tunjangan_Kompetensi_Q1.xlsx
+++ b/e2e/expectedData/moju_Tunjangan_Kompetensi_Q1.xlsx
@@ -128,7 +128,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
